--- a/KeywordDrivenTest/TestData/TestCases.xlsx
+++ b/KeywordDrivenTest/TestData/TestCases.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28318"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28502"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{27AD53BA-C06C-44DF-8C84-6DBF1A9FC933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF8FC66B-2EB7-41F8-8D88-B4220AA526F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -57,7 +57,7 @@
     <t>NavigateToURL</t>
   </si>
   <si>
-    <t>https://safv.stellasoftware.com/</t>
+    <t>https://www.google.com/</t>
   </si>
   <si>
     <t>Step2</t>
@@ -93,13 +93,10 @@
     <t>Step5</t>
   </si>
   <si>
-    <t>VerifyText</t>
-  </si>
-  <si>
-    <t>welcomeMessage</t>
-  </si>
-  <si>
-    <t>Welcome</t>
+    <t>VerifyPageTitle</t>
+  </si>
+  <si>
+    <t>Home Page - SAFV_Site</t>
   </si>
 </sst>
 </file>
@@ -152,10 +149,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -491,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
@@ -499,9 +497,12 @@
     <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="68.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -518,7 +519,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -532,7 +533,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -549,7 +550,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -566,7 +567,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -580,7 +581,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -590,12 +591,180 @@
       <c r="C6" t="s">
         <v>20</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>21</v>
       </c>
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="J13" s="3"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="J15" s="3"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="J16" s="3"/>
+    </row>
+    <row r="17" spans="10:10">
+      <c r="J17" s="3"/>
+    </row>
+    <row r="18" spans="10:10">
+      <c r="J18" s="3"/>
+    </row>
+    <row r="19" spans="10:10">
+      <c r="J19" s="3"/>
+    </row>
+    <row r="20" spans="10:10">
+      <c r="J20" s="3"/>
+    </row>
+    <row r="21" spans="10:10">
+      <c r="J21" s="3"/>
+    </row>
+    <row r="22" spans="10:10">
+      <c r="J22" s="3"/>
+    </row>
+    <row r="23" spans="10:10">
+      <c r="J23" s="3"/>
+    </row>
+    <row r="24" spans="10:10">
+      <c r="J24" s="3"/>
+    </row>
+    <row r="25" spans="10:10">
+      <c r="J25" s="3"/>
+    </row>
+    <row r="26" spans="10:10">
+      <c r="J26" s="3"/>
+    </row>
+    <row r="27" spans="10:10">
+      <c r="J27" s="3"/>
+    </row>
+    <row r="28" spans="10:10">
+      <c r="J28" s="3"/>
+    </row>
+    <row r="29" spans="10:10">
+      <c r="J29" s="3"/>
+    </row>
+    <row r="30" spans="10:10">
+      <c r="J30" s="3"/>
+    </row>
+    <row r="31" spans="10:10">
+      <c r="J31" s="3"/>
+    </row>
+    <row r="32" spans="10:10">
+      <c r="J32" s="3"/>
+    </row>
+    <row r="33" spans="10:10">
+      <c r="J33" s="3"/>
+    </row>
+    <row r="34" spans="10:10">
+      <c r="J34" s="3"/>
+    </row>
+    <row r="35" spans="10:10">
+      <c r="J35" s="3"/>
+    </row>
+    <row r="36" spans="10:10">
+      <c r="J36" s="3"/>
+    </row>
+    <row r="37" spans="10:10">
+      <c r="J37" s="3"/>
+    </row>
+    <row r="38" spans="10:10">
+      <c r="J38" s="3"/>
+    </row>
+    <row r="39" spans="10:10">
+      <c r="J39" s="3"/>
+    </row>
+    <row r="40" spans="10:10">
+      <c r="J40" s="3"/>
+    </row>
+    <row r="41" spans="10:10">
+      <c r="J41" s="3"/>
+    </row>
+    <row r="42" spans="10:10">
+      <c r="J42" s="3"/>
+    </row>
+    <row r="43" spans="10:10">
+      <c r="J43" s="3"/>
+    </row>
+    <row r="44" spans="10:10">
+      <c r="J44" s="3"/>
+    </row>
+    <row r="45" spans="10:10">
+      <c r="J45" s="3"/>
+    </row>
+    <row r="46" spans="10:10">
+      <c r="J46" s="3"/>
+    </row>
+    <row r="47" spans="10:10">
+      <c r="J47" s="3"/>
+    </row>
+    <row r="48" spans="10:10">
+      <c r="J48" s="3"/>
+    </row>
+    <row r="49" spans="10:10">
+      <c r="J49" s="3"/>
+    </row>
+    <row r="50" spans="10:10">
+      <c r="J50" s="3"/>
+    </row>
+    <row r="51" spans="10:10">
+      <c r="J51" s="3"/>
+    </row>
+    <row r="52" spans="10:10">
+      <c r="J52" s="3"/>
+    </row>
+    <row r="53" spans="10:10">
+      <c r="J53" s="3"/>
+    </row>
+    <row r="54" spans="10:10">
+      <c r="J54" s="3"/>
+    </row>
+    <row r="55" spans="10:10">
+      <c r="J55" s="3"/>
+    </row>
+    <row r="56" spans="10:10">
+      <c r="J56" s="3"/>
+    </row>
+    <row r="57" spans="10:10">
+      <c r="J57" s="3"/>
+    </row>
+    <row r="58" spans="10:10">
+      <c r="J58" s="3"/>
+    </row>
+    <row r="59" spans="10:10">
+      <c r="J59" s="3"/>
+    </row>
+    <row r="60" spans="10:10">
+      <c r="J60" s="3"/>
+    </row>
+    <row r="61" spans="10:10">
+      <c r="J61" s="3"/>
+    </row>
+    <row r="62" spans="10:10">
+      <c r="J62" s="3"/>
+    </row>
+    <row r="63" spans="10:10">
+      <c r="J63" s="3"/>
+    </row>
+    <row r="64" spans="10:10">
+      <c r="J64" s="3"/>
+    </row>
+    <row r="65" spans="10:10">
+      <c r="J65" s="3"/>
+    </row>
+    <row r="66" spans="10:10">
+      <c r="J66" s="3"/>
+    </row>
+    <row r="67" spans="10:10">
+      <c r="J67" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
